--- a/data/file_generation/input/data_198/2025年度上半年排课.xlsx
+++ b/data/file_generation/input/data_198/2025年度上半年排课.xlsx
@@ -13404,18 +13404,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1FF812B-8F33-4097-9F62-33291D852A38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C550B6-DE6F-4B03-BD39-61ABA515281A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FE181DD-7738-42BB-89A9-E74B017C4520}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65A3935B-5167-469A-91D3-0E5E7E49E910}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A53D1FD1-ABB4-430C-A50F-265F6585C7E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447F6EBE-08A7-40A1-B01B-743F8A1FF0FF}"/>
 </file>